--- a/countries/hk/2026-2029.xlsx
+++ b/countries/hk/2026-2029.xlsx
@@ -38145,13 +38145,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O252" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R252" t="n">
-        <v>0.4878973008708154</v>
+        <v>0.5150027064747495</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42128,13 +42128,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O277" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R277" t="n">
-        <v>1.043558115751466</v>
+        <v>1.030005412949499</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -47779,13 +47779,13 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O316" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R316" t="n">
-        <v>0.4065810840590128</v>
+        <v>0.4201337868609799</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -49332,13 +49332,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O326" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R326" t="n">
-        <v>0.06776351400983546</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -57413,13 +57413,13 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O380" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R380" t="n">
-        <v>0.4472391924649141</v>
+        <v>0.5150027064747495</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -67047,13 +67047,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O444" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R444" t="n">
-        <v>0.4065810840590128</v>
+        <v>0.4743445980688483</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -67658,6 +67658,9640 @@
         </is>
       </c>
       <c r="BC447" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR448" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr"/>
+      <c r="AT448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU448" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV448" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW448" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX448" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA448" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB448" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC448" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0</v>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR449" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr"/>
+      <c r="AT449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0</v>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO450" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR450" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS450" t="inlineStr"/>
+      <c r="AT450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU450" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV450" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW450" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA450" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB450" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC450" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>199</v>
+      </c>
+      <c r="O451" t="n">
+        <v>199</v>
+      </c>
+      <c r="R451" t="n">
+        <v>2.696987857591452</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR451" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr"/>
+      <c r="AT451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV451" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW451" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX451" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY451" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA451" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB451" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC451" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>4</v>
+      </c>
+      <c r="O452" t="n">
+        <v>4</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0.05421081120786837</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR452" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr"/>
+      <c r="AT452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU452" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV452" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW452" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX452" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY452" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA452" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB452" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC452" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="R453" t="n">
+        <v>0</v>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO453" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP453" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR453" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS453" t="inlineStr"/>
+      <c r="AT453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU453" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV453" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW453" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX453" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY453" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA453" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB453" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC453" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>3</v>
+      </c>
+      <c r="O454" t="n">
+        <v>3</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0.04065810840590128</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR454" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS454" t="inlineStr"/>
+      <c r="AT454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU454" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV454" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW454" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX454" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY454" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA454" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB454" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC454" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="R455" t="n">
+        <v>0</v>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO455" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP455" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR455" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS455" t="inlineStr"/>
+      <c r="AT455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU455" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV455" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW455" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX455" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY455" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA455" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB455" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC455" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>9</v>
+      </c>
+      <c r="O456" t="n">
+        <v>9</v>
+      </c>
+      <c r="R456" t="n">
+        <v>0.1219743252177038</v>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO456" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP456" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR456" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS456" t="inlineStr"/>
+      <c r="AT456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU456" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV456" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW456" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX456" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY456" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA456" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB456" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC456" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
+      <c r="R457" t="n">
+        <v>0</v>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO457" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP457" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR457" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS457" t="inlineStr"/>
+      <c r="AT457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU457" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV457" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW457" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX457" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY457" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA457" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB457" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC457" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H5)</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB458" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC458" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD458" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE458" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF458" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG458" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI458" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ458" t="inlineStr">
+        <is>
+          <t>HK_CHP_H5_current</t>
+        </is>
+      </c>
+      <c r="AK458" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H5 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM458" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN458" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO458" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP458" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ458" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS458" t="inlineStr"/>
+      <c r="AT458" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU458" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV458" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW458" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX458" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY458" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA458" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB458" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC458" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
+        </is>
+      </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H7)</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB459" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC459" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD459" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE459" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF459" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG459" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI459" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ459" t="inlineStr">
+        <is>
+          <t>HK_CHP_H7_current</t>
+        </is>
+      </c>
+      <c r="AK459" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H7 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM459" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN459" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO459" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP459" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ459" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS459" t="inlineStr"/>
+      <c r="AT459" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU459" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV459" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW459" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX459" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY459" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA459" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB459" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC459" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
+        </is>
+      </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>Novel influenza A infection - Others</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB460" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC460" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD460" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE460" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF460" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG460" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI460" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ460" t="inlineStr">
+        <is>
+          <t>HK_CHP_other_current</t>
+        </is>
+      </c>
+      <c r="AK460" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP residual novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM460" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN460" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO460" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP460" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ460" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS460" t="inlineStr"/>
+      <c r="AT460" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU460" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV460" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW460" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX460" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY460" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA460" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB460" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC460" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" t="n">
+        <v>1</v>
+      </c>
+      <c r="R461" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO461" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP461" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR461" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS461" t="inlineStr"/>
+      <c r="AT461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU461" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV461" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW461" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX461" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY461" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA461" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB461" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC461" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0</v>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO462" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP462" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR462" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS462" t="inlineStr"/>
+      <c r="AT462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU462" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV462" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW462" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX462" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY462" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA462" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB462" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC462" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0</v>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO463" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP463" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR463" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS463" t="inlineStr"/>
+      <c r="AT463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU463" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV463" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW463" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX463" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY463" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA463" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB463" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC463" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N464" t="n">
+        <v>1</v>
+      </c>
+      <c r="O464" t="n">
+        <v>1</v>
+      </c>
+      <c r="R464" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO464" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP464" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR464" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS464" t="inlineStr"/>
+      <c r="AT464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU464" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV464" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW464" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX464" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY464" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA464" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB464" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC464" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N465" t="n">
+        <v>0</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0</v>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO465" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP465" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR465" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS465" t="inlineStr"/>
+      <c r="AT465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU465" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV465" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW465" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX465" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY465" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA465" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB465" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC465" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N466" t="n">
+        <v>227</v>
+      </c>
+      <c r="O466" t="n">
+        <v>227</v>
+      </c>
+      <c r="R466" t="n">
+        <v>3.07646353604653</v>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO466" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP466" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR466" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS466" t="inlineStr"/>
+      <c r="AT466" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU466" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV466" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW466" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX466" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY466" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA466" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB466" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC466" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N467" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="R467" t="n">
+        <v>0</v>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO467" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP467" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR467" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS467" t="inlineStr"/>
+      <c r="AT467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU467" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV467" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW467" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX467" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY467" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA467" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB467" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC467" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>0</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO468" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP468" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR468" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS468" t="inlineStr"/>
+      <c r="AT468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU468" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV468" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW468" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX468" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY468" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA468" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB468" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC468" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N469" t="n">
+        <v>27</v>
+      </c>
+      <c r="O469" t="n">
+        <v>27</v>
+      </c>
+      <c r="R469" t="n">
+        <v>0.3659229756531115</v>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO469" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP469" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR469" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS469" t="inlineStr"/>
+      <c r="AT469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU469" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV469" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW469" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX469" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY469" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA469" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB469" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC469" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>1</v>
+      </c>
+      <c r="O470" t="n">
+        <v>1</v>
+      </c>
+      <c r="R470" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO470" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP470" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR470" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS470" t="inlineStr"/>
+      <c r="AT470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU470" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV470" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW470" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX470" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY470" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA470" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB470" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC470" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>3</v>
+      </c>
+      <c r="O471" t="n">
+        <v>3</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0.04065810840590128</v>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO471" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP471" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR471" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS471" t="inlineStr"/>
+      <c r="AT471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU471" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV471" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW471" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX471" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY471" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA471" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB471" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC471" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>2</v>
+      </c>
+      <c r="O472" t="n">
+        <v>2</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO472" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP472" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR472" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS472" t="inlineStr"/>
+      <c r="AT472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU472" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV472" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW472" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX472" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY472" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA472" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB472" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC472" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="R473" t="n">
+        <v>0</v>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO473" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP473" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR473" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS473" t="inlineStr"/>
+      <c r="AT473" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU473" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV473" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW473" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX473" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY473" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA473" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB473" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC473" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0</v>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO474" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP474" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR474" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS474" t="inlineStr"/>
+      <c r="AT474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU474" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV474" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW474" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX474" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY474" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA474" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB474" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC474" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>0</v>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO475" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP475" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR475" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS475" t="inlineStr"/>
+      <c r="AT475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU475" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV475" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW475" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX475" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY475" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA475" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB475" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC475" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="R476" t="n">
+        <v>0</v>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO476" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP476" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR476" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS476" t="inlineStr"/>
+      <c r="AT476" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU476" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV476" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW476" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX476" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY476" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA476" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB476" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC476" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0</v>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR477" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS477" t="inlineStr"/>
+      <c r="AT477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU477" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV477" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW477" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX477" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY477" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA477" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB477" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC477" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N478" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
+      <c r="R478" t="n">
+        <v>0</v>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO478" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP478" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR478" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS478" t="inlineStr"/>
+      <c r="AT478" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU478" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV478" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW478" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX478" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY478" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA478" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB478" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC478" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N479" t="n">
+        <v>121</v>
+      </c>
+      <c r="O479" t="n">
+        <v>121</v>
+      </c>
+      <c r="R479" t="n">
+        <v>1.639877039038018</v>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO479" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP479" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR479" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS479" t="inlineStr"/>
+      <c r="AT479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU479" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV479" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW479" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX479" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY479" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA479" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB479" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC479" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>1</v>
+      </c>
+      <c r="O480" t="n">
+        <v>1</v>
+      </c>
+      <c r="R480" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO480" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP480" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR480" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS480" t="inlineStr"/>
+      <c r="AT480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU480" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV480" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW480" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX480" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY480" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA480" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB480" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC480" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N481" t="n">
+        <v>1</v>
+      </c>
+      <c r="O481" t="n">
+        <v>1</v>
+      </c>
+      <c r="R481" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO481" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP481" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR481" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS481" t="inlineStr"/>
+      <c r="AT481" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU481" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV481" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW481" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX481" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY481" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA481" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB481" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC481" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N482" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
+      <c r="R482" t="n">
+        <v>0</v>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO482" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP482" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR482" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS482" t="inlineStr"/>
+      <c r="AT482" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU482" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV482" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW482" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX482" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY482" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA482" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB482" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC482" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N483" t="n">
+        <v>0</v>
+      </c>
+      <c r="O483" t="n">
+        <v>0</v>
+      </c>
+      <c r="R483" t="n">
+        <v>0</v>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO483" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP483" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR483" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS483" t="inlineStr"/>
+      <c r="AT483" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU483" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV483" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW483" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX483" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY483" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA483" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB483" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC483" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N484" t="n">
+        <v>4</v>
+      </c>
+      <c r="O484" t="n">
+        <v>4</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0.05421081120786837</v>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO484" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP484" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR484" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS484" t="inlineStr"/>
+      <c r="AT484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU484" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV484" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW484" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX484" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY484" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA484" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB484" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC484" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N485" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="R485" t="n">
+        <v>0</v>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO485" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP485" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR485" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS485" t="inlineStr"/>
+      <c r="AT485" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU485" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV485" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW485" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX485" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY485" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA485" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB485" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC485" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N486" t="n">
+        <v>0</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="R486" t="n">
+        <v>0</v>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO486" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP486" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR486" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS486" t="inlineStr"/>
+      <c r="AT486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU486" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV486" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW486" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX486" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY486" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA486" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB486" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC486" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N487" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO487" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP487" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR487" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS487" t="inlineStr"/>
+      <c r="AT487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU487" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV487" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW487" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX487" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY487" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA487" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB487" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC487" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="R488" t="n">
+        <v>0</v>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO488" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP488" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR488" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS488" t="inlineStr"/>
+      <c r="AT488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU488" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV488" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW488" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX488" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY488" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA488" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB488" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC488" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N489" t="n">
+        <v>7</v>
+      </c>
+      <c r="O489" t="n">
+        <v>7</v>
+      </c>
+      <c r="R489" t="n">
+        <v>0.09486891961376966</v>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO489" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP489" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR489" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS489" t="inlineStr"/>
+      <c r="AT489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU489" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV489" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW489" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX489" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY489" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA489" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB489" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC489" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N490" t="n">
+        <v>31</v>
+      </c>
+      <c r="O490" t="n">
+        <v>31</v>
+      </c>
+      <c r="R490" t="n">
+        <v>0.4201337868609799</v>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO490" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP490" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR490" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS490" t="inlineStr"/>
+      <c r="AT490" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU490" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV490" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW490" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX490" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY490" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA490" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB490" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC490" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N491" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO491" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP491" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR491" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS491" t="inlineStr"/>
+      <c r="AT491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU491" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV491" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW491" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX491" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY491" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA491" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB491" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC491" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N492" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>0</v>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO492" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP492" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR492" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS492" t="inlineStr"/>
+      <c r="AT492" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU492" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV492" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW492" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX492" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY492" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA492" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB492" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC492" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N493" t="n">
+        <v>2</v>
+      </c>
+      <c r="O493" t="n">
+        <v>2</v>
+      </c>
+      <c r="R493" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO493" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP493" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR493" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS493" t="inlineStr"/>
+      <c r="AT493" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU493" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV493" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW493" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX493" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY493" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA493" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB493" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC493" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N494" t="n">
+        <v>0</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="R494" t="n">
+        <v>0</v>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO494" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP494" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR494" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS494" t="inlineStr"/>
+      <c r="AT494" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU494" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV494" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW494" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX494" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY494" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA494" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB494" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC494" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N495" t="n">
+        <v>1</v>
+      </c>
+      <c r="O495" t="n">
+        <v>1</v>
+      </c>
+      <c r="R495" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO495" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP495" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR495" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS495" t="inlineStr"/>
+      <c r="AT495" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU495" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV495" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW495" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX495" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY495" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA495" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB495" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC495" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N496" t="n">
+        <v>1</v>
+      </c>
+      <c r="O496" t="n">
+        <v>1</v>
+      </c>
+      <c r="R496" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO496" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP496" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR496" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS496" t="inlineStr"/>
+      <c r="AT496" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU496" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV496" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW496" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX496" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY496" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA496" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB496" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC496" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>斑点热立克次体病</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N497" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO497" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP497" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR497" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS497" t="inlineStr"/>
+      <c r="AT497" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU497" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV497" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW497" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX497" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY497" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA497" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB497" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC497" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N498" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO498" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP498" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR498" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS498" t="inlineStr"/>
+      <c r="AT498" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU498" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV498" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW498" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX498" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY498" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA498" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB498" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC498" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N499" t="n">
+        <v>2</v>
+      </c>
+      <c r="O499" t="n">
+        <v>2</v>
+      </c>
+      <c r="R499" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO499" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP499" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR499" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS499" t="inlineStr"/>
+      <c r="AT499" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU499" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV499" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW499" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX499" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY499" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA499" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB499" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC499" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N500" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO500" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP500" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR500" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS500" t="inlineStr"/>
+      <c r="AT500" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU500" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV500" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW500" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX500" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY500" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA500" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB500" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC500" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N501" t="n">
+        <v>0</v>
+      </c>
+      <c r="O501" t="n">
+        <v>0</v>
+      </c>
+      <c r="R501" t="n">
+        <v>0</v>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO501" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP501" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR501" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS501" t="inlineStr"/>
+      <c r="AT501" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU501" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV501" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW501" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX501" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY501" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA501" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB501" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC501" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N502" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO502" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP502" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR502" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS502" t="inlineStr"/>
+      <c r="AT502" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU502" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV502" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW502" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX502" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY502" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA502" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB502" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC502" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N503" t="n">
+        <v>0</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="R503" t="n">
+        <v>0</v>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO503" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP503" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR503" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS503" t="inlineStr"/>
+      <c r="AT503" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU503" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV503" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW503" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX503" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY503" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA503" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB503" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC503" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N504" t="n">
+        <v>1</v>
+      </c>
+      <c r="O504" t="n">
+        <v>1</v>
+      </c>
+      <c r="R504" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO504" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP504" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR504" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS504" t="inlineStr"/>
+      <c r="AT504" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU504" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV504" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW504" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX504" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY504" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA504" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB504" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC504" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N505" t="n">
+        <v>0</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO505" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP505" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR505" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS505" t="inlineStr"/>
+      <c r="AT505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU505" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV505" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW505" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX505" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY505" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA505" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB505" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC505" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N506" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="R506" t="n">
+        <v>0</v>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO506" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP506" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR506" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS506" t="inlineStr"/>
+      <c r="AT506" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU506" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV506" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW506" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX506" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY506" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA506" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB506" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC506" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>D196</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Foodborne disease outbreak</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>食源性疾病暴发</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N507" t="n">
+        <v>6</v>
+      </c>
+      <c r="O507" t="n">
+        <v>6</v>
+      </c>
+      <c r="R507" t="n">
+        <v>0.08131621681180255</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO507" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP507" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR507" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS507" t="inlineStr"/>
+      <c r="AT507" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU507" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV507" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW507" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX507" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY507" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA507" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB507" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC507" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>D206</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Community-associated methicillin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>社区相关耐甲氧西林金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N508" t="n">
+        <v>20</v>
+      </c>
+      <c r="O508" t="n">
+        <v>20</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0.2710540560393419</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO508" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP508" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR508" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS508" t="inlineStr"/>
+      <c r="AT508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU508" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV508" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW508" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX508" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY508" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA508" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB508" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC508" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>D207</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Enterovirus 71 infection</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>肠病毒71型感染</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N509" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="R509" t="n">
+        <v>0</v>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO509" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP509" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR509" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS509" t="inlineStr"/>
+      <c r="AT509" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU509" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV509" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW509" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX509" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY509" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA509" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB509" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC509" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N510" t="n">
+        <v>1</v>
+      </c>
+      <c r="O510" t="n">
+        <v>1</v>
+      </c>
+      <c r="R510" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO510" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP510" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ510" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS510" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT510" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU510" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV510" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW510" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX510" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY510" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA510" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB510" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC510" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N511" t="n">
+        <v>1</v>
+      </c>
+      <c r="O511" t="n">
+        <v>1</v>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB511" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC511" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD511" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE511" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF511" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG511" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH511" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI511" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ511" t="inlineStr">
+        <is>
+          <t>HK_CHP_current</t>
+        </is>
+      </c>
+      <c r="AK511" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM511" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN511" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO511" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP511" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ511" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS511" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT511" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU511" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV511" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW511" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX511" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY511" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA511" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB511" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC511" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -67696,7 +77330,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -67779,7 +77413,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -67789,7 +77423,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>446</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11">
@@ -67809,7 +77443,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -67841,7 +77475,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4402</v>
+        <v>5089</v>
       </c>
     </row>
     <row r="16">
